--- a/res/LOL - Dmg Calculator.xlsx
+++ b/res/LOL - Dmg Calculator.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21901"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB3F53C-3EFF-4F55-A190-CD4630F6237E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1CEF0AE-02DE-4778-A88C-D8D074AB458F}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="28">
   <si>
     <t>Lvl</t>
   </si>
@@ -193,14 +194,41 @@
     </r>
   </si>
   <si>
-    <t>Yunus Emre Ak</t>
+    <t>AP</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">NAUTİLUS ( </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>In progress</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> )</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -235,6 +263,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="4"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -413,7 +449,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -424,88 +460,85 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -802,30 +835,30 @@
   <sheetData>
     <row r="4" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="11"/>
-      <c r="R5" s="9" t="s">
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="24"/>
+      <c r="R5" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="S5" s="10"/>
-      <c r="T5" s="10"/>
-      <c r="U5" s="10"/>
-      <c r="V5" s="10"/>
-      <c r="W5" s="10"/>
-      <c r="X5" s="10"/>
-      <c r="Y5" s="10"/>
-      <c r="Z5" s="10"/>
-      <c r="AA5" s="11"/>
+      <c r="S5" s="23"/>
+      <c r="T5" s="23"/>
+      <c r="U5" s="23"/>
+      <c r="V5" s="23"/>
+      <c r="W5" s="23"/>
+      <c r="X5" s="23"/>
+      <c r="Y5" s="23"/>
+      <c r="Z5" s="23"/>
+      <c r="AA5" s="24"/>
     </row>
     <row r="6" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
@@ -833,793 +866,920 @@
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="3"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="14"/>
-      <c r="R6" s="12"/>
-      <c r="S6" s="13"/>
-      <c r="T6" s="13"/>
-      <c r="U6" s="13"/>
-      <c r="V6" s="13"/>
-      <c r="W6" s="13"/>
-      <c r="X6" s="13"/>
-      <c r="Y6" s="13"/>
-      <c r="Z6" s="13"/>
-      <c r="AA6" s="14"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="26"/>
+      <c r="M6" s="26"/>
+      <c r="N6" s="26"/>
+      <c r="O6" s="26"/>
+      <c r="P6" s="27"/>
+      <c r="R6" s="25"/>
+      <c r="S6" s="26"/>
+      <c r="T6" s="26"/>
+      <c r="U6" s="26"/>
+      <c r="V6" s="26"/>
+      <c r="W6" s="26"/>
+      <c r="X6" s="26"/>
+      <c r="Y6" s="26"/>
+      <c r="Z6" s="26"/>
+      <c r="AA6" s="27"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="15">
         <f>65.25+N11*3.75</f>
         <v>72.75</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K7" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="L7" s="5" t="s">
+      <c r="L7" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="M7" s="5" t="s">
+      <c r="M7" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="N7" s="5" t="s">
+      <c r="N7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="O7" s="5" t="s">
+      <c r="O7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="P7" s="5" t="s">
+      <c r="P7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="R7" s="5" t="s">
+      <c r="R7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S7" s="7">
+      <c r="S7" s="15">
         <f>65.25+Y11*3.75</f>
         <v>65.25</v>
       </c>
-      <c r="T7" s="5" t="s">
+      <c r="T7" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="U7" s="5" t="s">
+      <c r="U7" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="V7" s="5" t="s">
+      <c r="V7" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="W7" s="5" t="s">
+      <c r="W7" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="X7" s="5" t="s">
+      <c r="X7" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="Y7" s="5" t="s">
+      <c r="Y7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="Z7" s="5" t="s">
+      <c r="Z7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="AA7" s="5" t="s">
+      <c r="AA7" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G8" s="6"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="17"/>
-      <c r="T8" s="6"/>
-      <c r="U8" s="6"/>
-      <c r="V8" s="6"/>
-      <c r="W8" s="6"/>
-      <c r="X8" s="6"/>
-      <c r="Y8" s="6"/>
-      <c r="Z8" s="6"/>
-      <c r="AA8" s="6"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="16"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7"/>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="7"/>
+      <c r="Z8" s="7"/>
+      <c r="AA8" s="7"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="15">
+      <c r="H9" s="20">
         <v>25</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9" s="15">
         <f>H7+H9</f>
         <v>97.75</v>
       </c>
-      <c r="J9" s="7">
+      <c r="J9" s="15">
         <f>IF(J11,IF(J13, 50, 35) + IF(J13,50, 30) *J11 + IF(J13,1.2, 0.8)*H9,0)</f>
         <v>130</v>
       </c>
-      <c r="K9" s="7">
+      <c r="K9" s="15">
         <f>IF(K11,(-5+10*K11+0.75*I9) *IF(K13,3, 2),0)</f>
         <v>156.625</v>
       </c>
-      <c r="L9" s="7">
+      <c r="L9" s="15">
         <f>IF(L11, 10 + 30 * L11 + 0.9 * H9 + IF(L13, 25, 10) + IF(L13, 45, 30) * L11 + IF(L13, 1.35, 0.9)*H9, 0)</f>
         <v>0</v>
       </c>
-      <c r="M9" s="7" t="str">
+      <c r="M9" s="15" t="str">
         <f>IF(M11, _xlfn.CONCAT(250*M11, " HP"), _xlfn.CONCAT("Yok"))</f>
         <v>Yok</v>
       </c>
-      <c r="N9" s="7">
+      <c r="N9" s="15">
         <f>I9*I11 + J9+K9+L9</f>
         <v>286.625</v>
       </c>
-      <c r="O9" s="7">
+      <c r="O9" s="15">
         <f>IF(P15&gt;=0,(100/(100+P15)*N9),(2 - 100/(100 -(P15))) * N9)</f>
         <v>143.3125</v>
       </c>
-      <c r="P9" s="7">
+      <c r="P9" s="15">
         <f>O9+M13+N13</f>
         <v>283.3125</v>
       </c>
-      <c r="R9" s="5" t="s">
+      <c r="R9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="S9" s="15">
-        <v>0</v>
-      </c>
-      <c r="T9" s="7">
+      <c r="S9" s="20">
+        <v>0</v>
+      </c>
+      <c r="T9" s="15">
         <f>S7+S9</f>
         <v>65.25</v>
       </c>
-      <c r="U9" s="7">
+      <c r="U9" s="15">
         <f>10 + 20 *U11</f>
         <v>10</v>
       </c>
-      <c r="V9" s="7" t="str">
+      <c r="V9" s="15" t="str">
         <f>_xlfn.CONCAT("%", (35 + 12* V11))</f>
         <v>%35</v>
       </c>
-      <c r="W9" s="7">
+      <c r="W9" s="15">
         <f>IF(W11, 10 + 30 * W11 + 0.9 * S9 + IF(W13, 25, 10) + IF(W13, 45, 30) * W11 + IF(W13, 1.35, 0.9)*S9, 0)</f>
         <v>0</v>
       </c>
-      <c r="X9" s="7" t="str">
+      <c r="X9" s="15" t="str">
         <f>IF(X11, _xlfn.CONCAT(250*X11, " HP"), _xlfn.CONCAT("Yok"))</f>
         <v>Yok</v>
       </c>
-      <c r="Y9" s="7">
+      <c r="Y9" s="15">
         <f>T9*T11 + U9+V9+W9</f>
         <v>75.599999999999994</v>
       </c>
-      <c r="Z9" s="7">
+      <c r="Z9" s="15">
         <f>Y9+X13+Y13</f>
         <v>155.6</v>
       </c>
-      <c r="AA9" s="7">
+      <c r="AA9" s="15">
         <f>IF(AA15&gt;=0,(100/(100+AA15)*Y9),(2 - 100/(100 -(AA15))) * Y9)</f>
         <v>50.399999999999991</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G10" s="6"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="8"/>
-      <c r="R10" s="6"/>
-      <c r="S10" s="16"/>
-      <c r="T10" s="17"/>
-      <c r="U10" s="17"/>
-      <c r="V10" s="17"/>
-      <c r="W10" s="17"/>
-      <c r="X10" s="17"/>
-      <c r="Y10" s="17"/>
-      <c r="Z10" s="8"/>
-      <c r="AA10" s="8"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="21"/>
+      <c r="T10" s="16"/>
+      <c r="U10" s="16"/>
+      <c r="V10" s="16"/>
+      <c r="W10" s="16"/>
+      <c r="X10" s="16"/>
+      <c r="Y10" s="16"/>
+      <c r="Z10" s="19"/>
+      <c r="AA10" s="19"/>
     </row>
     <row r="11" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H11" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="I11" s="15">
-        <v>0</v>
-      </c>
-      <c r="J11" s="15">
+      <c r="H11" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="I11" s="20">
+        <v>0</v>
+      </c>
+      <c r="J11" s="20">
         <v>1</v>
       </c>
-      <c r="K11" s="15">
+      <c r="K11" s="20">
         <v>1</v>
       </c>
-      <c r="L11" s="15">
-        <v>0</v>
-      </c>
-      <c r="M11" s="15">
-        <v>0</v>
-      </c>
-      <c r="N11" s="18">
+      <c r="L11" s="20">
+        <v>0</v>
+      </c>
+      <c r="M11" s="20">
+        <v>0</v>
+      </c>
+      <c r="N11" s="17">
         <f>J11+K11+L11+M11</f>
         <v>2</v>
       </c>
-      <c r="O11" s="20" t="s">
+      <c r="O11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="P11" s="21">
+      <c r="P11" s="5">
         <v>100</v>
       </c>
-      <c r="S11" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="T11" s="15">
+      <c r="S11" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="T11" s="20">
         <v>1</v>
       </c>
-      <c r="U11" s="15">
-        <v>0</v>
-      </c>
-      <c r="V11" s="15">
-        <v>0</v>
-      </c>
-      <c r="W11" s="15">
-        <v>0</v>
-      </c>
-      <c r="X11" s="15">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="18">
+      <c r="U11" s="20">
+        <v>0</v>
+      </c>
+      <c r="V11" s="20">
+        <v>0</v>
+      </c>
+      <c r="W11" s="20">
+        <v>0</v>
+      </c>
+      <c r="X11" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="17">
         <f>U11+V11+W11+X11</f>
         <v>0</v>
       </c>
-      <c r="Z11" s="20" t="s">
+      <c r="Z11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AA11" s="21">
+      <c r="AA11" s="5">
         <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H12" s="6"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="19"/>
-      <c r="O12" s="20"/>
-      <c r="P12" s="21"/>
-      <c r="S12" s="6"/>
-      <c r="T12" s="16"/>
-      <c r="U12" s="16"/>
-      <c r="V12" s="16"/>
-      <c r="W12" s="16"/>
-      <c r="X12" s="16"/>
-      <c r="Y12" s="19"/>
-      <c r="Z12" s="20"/>
-      <c r="AA12" s="21"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="21"/>
+      <c r="M12" s="21"/>
+      <c r="N12" s="18"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="5"/>
+      <c r="S12" s="7"/>
+      <c r="T12" s="21"/>
+      <c r="U12" s="21"/>
+      <c r="V12" s="21"/>
+      <c r="W12" s="21"/>
+      <c r="X12" s="21"/>
+      <c r="Y12" s="18"/>
+      <c r="Z12" s="4"/>
+      <c r="AA12" s="5"/>
     </row>
     <row r="13" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="J13" s="25">
+      <c r="J13" s="11">
         <v>1</v>
       </c>
-      <c r="K13" s="25">
-        <v>0</v>
-      </c>
-      <c r="L13" s="25">
-        <v>0</v>
-      </c>
-      <c r="M13" s="7">
+      <c r="K13" s="11">
+        <v>0</v>
+      </c>
+      <c r="L13" s="11">
+        <v>0</v>
+      </c>
+      <c r="M13" s="15">
         <f>50 + 20 *N11</f>
         <v>90</v>
       </c>
-      <c r="N13" s="18">
+      <c r="N13" s="17">
         <f>30 + 10 *N11</f>
         <v>50</v>
       </c>
-      <c r="O13" s="20" t="s">
+      <c r="O13" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="P13" s="21">
-        <v>0</v>
-      </c>
-      <c r="T13" s="5" t="s">
+      <c r="P13" s="5">
+        <v>0</v>
+      </c>
+      <c r="T13" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="U13" s="27">
-        <v>0</v>
-      </c>
-      <c r="V13" s="25">
+      <c r="U13" s="28">
+        <v>0</v>
+      </c>
+      <c r="V13" s="11">
         <v>1</v>
       </c>
-      <c r="W13" s="25">
-        <v>0</v>
-      </c>
-      <c r="X13" s="7">
+      <c r="W13" s="11">
+        <v>0</v>
+      </c>
+      <c r="X13" s="15">
         <f>50 + 20 *Y11</f>
         <v>50</v>
       </c>
-      <c r="Y13" s="18">
+      <c r="Y13" s="17">
         <f>30 + 10 *Y11</f>
         <v>30</v>
       </c>
-      <c r="Z13" s="20" t="s">
+      <c r="Z13" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="AA13" s="21">
+      <c r="AA13" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="I14" s="6"/>
-      <c r="J14" s="26"/>
-      <c r="K14" s="26"/>
-      <c r="L14" s="26"/>
-      <c r="M14" s="17"/>
-      <c r="N14" s="19"/>
-      <c r="O14" s="20"/>
-      <c r="P14" s="21"/>
-      <c r="T14" s="6"/>
-      <c r="U14" s="28"/>
-      <c r="V14" s="26"/>
-      <c r="W14" s="26"/>
-      <c r="X14" s="17"/>
-      <c r="Y14" s="19"/>
-      <c r="Z14" s="20"/>
-      <c r="AA14" s="21"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="5"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="29"/>
+      <c r="V14" s="12"/>
+      <c r="W14" s="12"/>
+      <c r="X14" s="16"/>
+      <c r="Y14" s="18"/>
+      <c r="Z14" s="4"/>
+      <c r="AA14" s="5"/>
     </row>
     <row r="15" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M15" s="5" t="s">
+      <c r="M15" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="N15" s="23" t="s">
+      <c r="N15" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="O15" s="20" t="s">
+      <c r="O15" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="P15" s="22">
+      <c r="P15" s="10">
         <f>P11-P13</f>
         <v>100</v>
       </c>
-      <c r="X15" s="5" t="s">
+      <c r="X15" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="Y15" s="23" t="s">
+      <c r="Y15" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="Z15" s="20" t="s">
+      <c r="Z15" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="AA15" s="22">
+      <c r="AA15" s="10">
         <f>AA11-AA13</f>
         <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M16" s="6"/>
-      <c r="N16" s="24"/>
-      <c r="O16" s="20"/>
-      <c r="P16" s="22"/>
-      <c r="X16" s="6"/>
-      <c r="Y16" s="24"/>
-      <c r="Z16" s="20"/>
-      <c r="AA16" s="22"/>
-    </row>
-    <row r="18" spans="7:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="7:26" x14ac:dyDescent="0.25">
-      <c r="G19" s="9" t="s">
+      <c r="M16" s="7"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="10"/>
+      <c r="X16" s="7"/>
+      <c r="Y16" s="9"/>
+      <c r="Z16" s="4"/>
+      <c r="AA16" s="10"/>
+    </row>
+    <row r="18" spans="7:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="7:27" x14ac:dyDescent="0.25">
+      <c r="G19" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
-      <c r="O19" s="10"/>
-      <c r="P19" s="11"/>
-    </row>
-    <row r="20" spans="7:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G20" s="12"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="13"/>
-      <c r="M20" s="13"/>
-      <c r="N20" s="13"/>
-      <c r="O20" s="13"/>
-      <c r="P20" s="14"/>
-    </row>
-    <row r="21" spans="7:26" x14ac:dyDescent="0.25">
-      <c r="G21" s="5" t="s">
+      <c r="H19" s="23"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="23"/>
+      <c r="L19" s="23"/>
+      <c r="M19" s="23"/>
+      <c r="N19" s="23"/>
+      <c r="O19" s="23"/>
+      <c r="P19" s="24"/>
+      <c r="R19" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="S19" s="23"/>
+      <c r="T19" s="23"/>
+      <c r="U19" s="23"/>
+      <c r="V19" s="23"/>
+      <c r="W19" s="23"/>
+      <c r="X19" s="23"/>
+      <c r="Y19" s="23"/>
+      <c r="Z19" s="23"/>
+      <c r="AA19" s="24"/>
+    </row>
+    <row r="20" spans="7:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G20" s="25"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="26"/>
+      <c r="K20" s="26"/>
+      <c r="L20" s="26"/>
+      <c r="M20" s="26"/>
+      <c r="N20" s="26"/>
+      <c r="O20" s="26"/>
+      <c r="P20" s="27"/>
+      <c r="R20" s="25"/>
+      <c r="S20" s="26"/>
+      <c r="T20" s="26"/>
+      <c r="U20" s="26"/>
+      <c r="V20" s="26"/>
+      <c r="W20" s="26"/>
+      <c r="X20" s="26"/>
+      <c r="Y20" s="26"/>
+      <c r="Z20" s="26"/>
+      <c r="AA20" s="27"/>
+    </row>
+    <row r="21" spans="7:27" x14ac:dyDescent="0.25">
+      <c r="G21" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H21" s="7">
+      <c r="H21" s="15">
         <f>65.25+N25*3.75</f>
         <v>69</v>
       </c>
-      <c r="I21" s="5" t="s">
+      <c r="I21" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J21" s="5" t="s">
+      <c r="J21" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="K21" s="5" t="s">
+      <c r="K21" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="L21" s="5" t="s">
+      <c r="L21" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="M21" s="5" t="s">
+      <c r="M21" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="N21" s="5" t="s">
+      <c r="N21" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="O21" s="5" t="s">
+      <c r="O21" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="P21" s="5" t="s">
+      <c r="P21" s="6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="22" spans="7:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G22" s="6"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-    </row>
-    <row r="23" spans="7:26" x14ac:dyDescent="0.25">
-      <c r="G23" s="5" t="s">
+      <c r="R21" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="S21" s="15">
+        <f>61+Y25*3.3</f>
+        <v>67.599999999999994</v>
+      </c>
+      <c r="T21" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="U21" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="V21" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="X21" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y21" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z21" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA21" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="7:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G22" s="7"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
+      <c r="O22" s="7"/>
+      <c r="P22" s="7"/>
+      <c r="R22" s="7"/>
+      <c r="S22" s="16"/>
+      <c r="T22" s="7"/>
+      <c r="U22" s="7"/>
+      <c r="V22" s="7"/>
+      <c r="W22" s="7"/>
+      <c r="X22" s="7"/>
+      <c r="Y22" s="7"/>
+      <c r="Z22" s="7"/>
+      <c r="AA22" s="7"/>
+    </row>
+    <row r="23" spans="7:27" x14ac:dyDescent="0.25">
+      <c r="G23" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H23" s="15">
-        <v>0</v>
-      </c>
-      <c r="I23" s="7">
+      <c r="H23" s="20">
+        <v>0</v>
+      </c>
+      <c r="I23" s="15">
         <f>H21+H23</f>
         <v>69</v>
       </c>
-      <c r="J23" s="7">
+      <c r="J23" s="15">
         <f>IF(J25, 30 + 25 *J25 + 0.8 *H23, 0)</f>
         <v>55</v>
       </c>
-      <c r="K23" s="7">
+      <c r="K23" s="15">
         <f xml:space="preserve"> IF(K25, 2.5 + 1.5 * K25 + (1 * H23 / 35), 0)</f>
         <v>0</v>
       </c>
-      <c r="L23" s="7">
+      <c r="L23" s="15">
         <f xml:space="preserve"> IF(L25,- 10 + 20 * L25 + 1.1 * I23,0)</f>
         <v>0</v>
       </c>
-      <c r="M23" s="7">
+      <c r="M23" s="15">
         <f xml:space="preserve"> IF(M25, -25 + 175 * M25 + 1.1 * H23, 0)</f>
         <v>0</v>
       </c>
-      <c r="N23" s="7">
+      <c r="N23" s="15">
         <f>J23+L23 * L27 + M23</f>
         <v>55</v>
       </c>
-      <c r="O23" s="7">
+      <c r="O23" s="15">
         <f>N23+M27+N27</f>
         <v>165</v>
       </c>
-      <c r="P23" s="7">
+      <c r="P23" s="15">
         <f>IF(P29&gt;=0,(100/(100+P29)*N23),(2 - 100/(100 -(P29))) * N23)</f>
         <v>42.307692307692307</v>
       </c>
-    </row>
-    <row r="24" spans="7:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G24" s="6"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
-      <c r="M24" s="17"/>
-      <c r="N24" s="17"/>
-      <c r="O24" s="8"/>
-      <c r="P24" s="8"/>
-    </row>
-    <row r="25" spans="7:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H25" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="I25" s="15">
+      <c r="R23" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="S23" s="20">
+        <v>25</v>
+      </c>
+      <c r="T23" s="15">
+        <f>S21+S23</f>
+        <v>92.6</v>
+      </c>
+      <c r="U23" s="15">
+        <f>80+(50 * (U25-1)) + 0.9*S27</f>
+        <v>80</v>
+      </c>
+      <c r="V23" s="15">
+        <f>55 + (30 * (V25 - 1 )) * V27</f>
+        <v>55</v>
+      </c>
+      <c r="W23" s="15">
+        <f>IF(W25, 55 + (30 * (W27 - 1 )) * V27, 0)</f>
+        <v>55</v>
+      </c>
+      <c r="X23" s="15">
+        <f>IF(X25, 125 + 50 * (X25 -1), 0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="15">
+        <f>T23*T25 + U23+V23+W23</f>
+        <v>190</v>
+      </c>
+      <c r="Z23" s="15">
+        <f>IF(AA29&gt;=0,(100/(100+AA29)*Y23),(2 - 100/(100 -(AA29))) * Y23)</f>
+        <v>95</v>
+      </c>
+      <c r="AA23" s="15">
+        <f>Z23+X27+Y27</f>
+        <v>235</v>
+      </c>
+    </row>
+    <row r="24" spans="7:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G24" s="7"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="16"/>
+      <c r="K24" s="16"/>
+      <c r="L24" s="16"/>
+      <c r="M24" s="16"/>
+      <c r="N24" s="16"/>
+      <c r="O24" s="19"/>
+      <c r="P24" s="19"/>
+      <c r="R24" s="7"/>
+      <c r="S24" s="21"/>
+      <c r="T24" s="16"/>
+      <c r="U24" s="16"/>
+      <c r="V24" s="16"/>
+      <c r="W24" s="16"/>
+      <c r="X24" s="16"/>
+      <c r="Y24" s="16"/>
+      <c r="Z24" s="19"/>
+      <c r="AA24" s="19"/>
+    </row>
+    <row r="25" spans="7:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H25" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="I25" s="20">
         <v>1</v>
       </c>
-      <c r="J25" s="15">
+      <c r="J25" s="20">
         <v>1</v>
       </c>
-      <c r="K25" s="15">
-        <v>0</v>
-      </c>
-      <c r="L25" s="15">
-        <v>0</v>
-      </c>
-      <c r="M25" s="15">
-        <v>0</v>
-      </c>
-      <c r="N25" s="18">
+      <c r="K25" s="20">
+        <v>0</v>
+      </c>
+      <c r="L25" s="20">
+        <v>0</v>
+      </c>
+      <c r="M25" s="20">
+        <v>0</v>
+      </c>
+      <c r="N25" s="17">
         <f>J25+K25+L25+M25</f>
         <v>1</v>
       </c>
-      <c r="O25" s="20" t="s">
+      <c r="O25" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="P25" s="21">
+      <c r="P25" s="5">
         <v>50</v>
       </c>
-    </row>
-    <row r="26" spans="7:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H26" s="6"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="19"/>
-      <c r="O26" s="20"/>
-      <c r="P26" s="21"/>
-    </row>
-    <row r="27" spans="7:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="I27" s="5" t="s">
+      <c r="S25" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="T25" s="20">
+        <v>0</v>
+      </c>
+      <c r="U25" s="20">
+        <v>1</v>
+      </c>
+      <c r="V25" s="20">
+        <v>0</v>
+      </c>
+      <c r="W25" s="20">
+        <v>1</v>
+      </c>
+      <c r="X25" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="17">
+        <f>U25+V25+W25+X25</f>
+        <v>2</v>
+      </c>
+      <c r="Z25" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="AA25" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="7:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H26" s="7"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="21"/>
+      <c r="L26" s="21"/>
+      <c r="M26" s="21"/>
+      <c r="N26" s="18"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="5"/>
+      <c r="S26" s="7"/>
+      <c r="T26" s="21"/>
+      <c r="U26" s="21"/>
+      <c r="V26" s="21"/>
+      <c r="W26" s="21"/>
+      <c r="X26" s="21"/>
+      <c r="Y26" s="18"/>
+      <c r="Z26" s="4"/>
+      <c r="AA26" s="5"/>
+    </row>
+    <row r="27" spans="7:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I27" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="J27" s="25">
-        <v>0</v>
-      </c>
-      <c r="K27" s="29">
+      <c r="J27" s="11">
+        <v>0</v>
+      </c>
+      <c r="K27" s="13">
         <v>1</v>
       </c>
-      <c r="L27" s="29">
+      <c r="L27" s="13">
         <v>2</v>
       </c>
-      <c r="M27" s="7">
+      <c r="M27" s="15">
         <f>50 + 20 *N25</f>
         <v>70</v>
       </c>
-      <c r="N27" s="18">
+      <c r="N27" s="17">
         <f>30 + 10 *N25</f>
         <v>40</v>
       </c>
-      <c r="O27" s="20" t="s">
+      <c r="O27" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="P27" s="21">
+      <c r="P27" s="5">
         <v>20</v>
       </c>
-      <c r="X27" s="31" t="s">
+      <c r="R27" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="Y27" s="31"/>
-      <c r="Z27" s="31"/>
-    </row>
-    <row r="28" spans="7:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="I28" s="6"/>
-      <c r="J28" s="26"/>
-      <c r="K28" s="30"/>
-      <c r="L28" s="30"/>
-      <c r="M28" s="17"/>
-      <c r="N28" s="19"/>
-      <c r="O28" s="20"/>
-      <c r="P28" s="21"/>
-      <c r="X28" s="31"/>
-      <c r="Y28" s="31"/>
-      <c r="Z28" s="31"/>
-    </row>
-    <row r="29" spans="7:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M29" s="5" t="s">
+      <c r="S27" s="20">
+        <v>0</v>
+      </c>
+      <c r="T27" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="U27" s="11">
+        <v>0</v>
+      </c>
+      <c r="V27" s="11">
+        <v>0</v>
+      </c>
+      <c r="W27" s="11">
+        <v>1</v>
+      </c>
+      <c r="X27" s="15">
+        <f>50 + 20 *Y25</f>
+        <v>90</v>
+      </c>
+      <c r="Y27" s="17">
+        <f>30 + 10 *Y25</f>
+        <v>50</v>
+      </c>
+      <c r="Z27" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA27" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="7:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I28" s="7"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="16"/>
+      <c r="N28" s="18"/>
+      <c r="O28" s="4"/>
+      <c r="P28" s="5"/>
+      <c r="R28" s="7"/>
+      <c r="S28" s="21"/>
+      <c r="T28" s="7"/>
+      <c r="U28" s="12"/>
+      <c r="V28" s="12"/>
+      <c r="W28" s="12"/>
+      <c r="X28" s="16"/>
+      <c r="Y28" s="18"/>
+      <c r="Z28" s="4"/>
+      <c r="AA28" s="5"/>
+    </row>
+    <row r="29" spans="7:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M29" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="N29" s="23" t="s">
+      <c r="N29" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="O29" s="20" t="s">
+      <c r="O29" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="P29" s="22">
+      <c r="P29" s="10">
         <f>P25-P27</f>
         <v>30</v>
       </c>
-      <c r="X29" s="31"/>
-      <c r="Y29" s="31"/>
-      <c r="Z29" s="31"/>
-    </row>
-    <row r="30" spans="7:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M30" s="6"/>
-      <c r="N30" s="24"/>
-      <c r="O30" s="20"/>
-      <c r="P30" s="22"/>
+      <c r="X29" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z29" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA29" s="10">
+        <f>AA25-AA27</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="7:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M30" s="7"/>
+      <c r="N30" s="9"/>
+      <c r="O30" s="4"/>
+      <c r="P30" s="10"/>
+      <c r="X30" s="7"/>
+      <c r="Y30" s="9"/>
+      <c r="Z30" s="4"/>
+      <c r="AA30" s="10"/>
     </row>
     <row r="34" spans="5:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" spans="5:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="4"/>
-      <c r="M35" s="4"/>
-      <c r="N35" s="4"/>
-      <c r="O35" s="4"/>
-      <c r="P35" s="4"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="30"/>
+      <c r="K35" s="30"/>
+      <c r="L35" s="30"/>
+      <c r="M35" s="30"/>
+      <c r="N35" s="30"/>
+      <c r="O35" s="30"/>
+      <c r="P35" s="30"/>
     </row>
     <row r="36" spans="5:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
-      <c r="M36" s="4"/>
-      <c r="N36" s="4"/>
-      <c r="O36" s="4"/>
-      <c r="P36" s="4"/>
+      <c r="F36" s="30"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="30"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="30"/>
+      <c r="K36" s="30"/>
+      <c r="L36" s="30"/>
+      <c r="M36" s="30"/>
+      <c r="N36" s="30"/>
+      <c r="O36" s="30"/>
+      <c r="P36" s="30"/>
     </row>
     <row r="37" spans="5:16" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="E37" s="4" t="s">
+      <c r="E37" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
-      <c r="N37" s="4"/>
-      <c r="O37" s="4"/>
-      <c r="P37" s="4"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="30"/>
+      <c r="N37" s="30"/>
+      <c r="O37" s="30"/>
+      <c r="P37" s="30"/>
     </row>
   </sheetData>
-  <mergeCells count="130">
-    <mergeCell ref="X27:Z29"/>
-    <mergeCell ref="O27:O28"/>
-    <mergeCell ref="P27:P28"/>
-    <mergeCell ref="M29:M30"/>
-    <mergeCell ref="N29:N30"/>
-    <mergeCell ref="O29:O30"/>
-    <mergeCell ref="P29:P30"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="J27:J28"/>
-    <mergeCell ref="K27:K28"/>
-    <mergeCell ref="L27:L28"/>
-    <mergeCell ref="M27:M28"/>
-    <mergeCell ref="N27:N28"/>
-    <mergeCell ref="P23:P24"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="K25:K26"/>
-    <mergeCell ref="L25:L26"/>
-    <mergeCell ref="M25:M26"/>
-    <mergeCell ref="N25:N26"/>
-    <mergeCell ref="O25:O26"/>
-    <mergeCell ref="P25:P26"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="K23:K24"/>
-    <mergeCell ref="L23:L24"/>
-    <mergeCell ref="M23:M24"/>
-    <mergeCell ref="N23:N24"/>
-    <mergeCell ref="O23:O24"/>
-    <mergeCell ref="G19:P20"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="K21:K22"/>
-    <mergeCell ref="L21:L22"/>
-    <mergeCell ref="M21:M22"/>
-    <mergeCell ref="N21:N22"/>
-    <mergeCell ref="O21:O22"/>
-    <mergeCell ref="P21:P22"/>
-    <mergeCell ref="Z13:Z14"/>
-    <mergeCell ref="AA13:AA14"/>
-    <mergeCell ref="X15:X16"/>
-    <mergeCell ref="Y15:Y16"/>
-    <mergeCell ref="Z15:Z16"/>
-    <mergeCell ref="AA15:AA16"/>
-    <mergeCell ref="T13:T14"/>
-    <mergeCell ref="U13:U14"/>
-    <mergeCell ref="V13:V14"/>
-    <mergeCell ref="W13:W14"/>
-    <mergeCell ref="X13:X14"/>
-    <mergeCell ref="Y13:Y14"/>
-    <mergeCell ref="AA9:AA10"/>
-    <mergeCell ref="S11:S12"/>
-    <mergeCell ref="T11:T12"/>
-    <mergeCell ref="U11:U12"/>
-    <mergeCell ref="V11:V12"/>
-    <mergeCell ref="W11:W12"/>
-    <mergeCell ref="X11:X12"/>
-    <mergeCell ref="Y11:Y12"/>
-    <mergeCell ref="Z11:Z12"/>
-    <mergeCell ref="AA11:AA12"/>
-    <mergeCell ref="R9:R10"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="V9:V10"/>
-    <mergeCell ref="W9:W10"/>
-    <mergeCell ref="X9:X10"/>
-    <mergeCell ref="Y9:Y10"/>
-    <mergeCell ref="Z9:Z10"/>
-    <mergeCell ref="R5:AA6"/>
-    <mergeCell ref="R7:R8"/>
-    <mergeCell ref="S7:S8"/>
-    <mergeCell ref="T7:T8"/>
-    <mergeCell ref="U7:U8"/>
-    <mergeCell ref="V7:V8"/>
-    <mergeCell ref="W7:W8"/>
-    <mergeCell ref="X7:X8"/>
-    <mergeCell ref="Y7:Y8"/>
-    <mergeCell ref="Z7:Z8"/>
-    <mergeCell ref="AA7:AA8"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="P11:P12"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="M7:M8"/>
-    <mergeCell ref="N7:N8"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="O15:O16"/>
-    <mergeCell ref="P15:P16"/>
-    <mergeCell ref="O11:O12"/>
-    <mergeCell ref="N15:N16"/>
-    <mergeCell ref="N13:N14"/>
+  <mergeCells count="173">
+    <mergeCell ref="AA27:AA28"/>
+    <mergeCell ref="X29:X30"/>
+    <mergeCell ref="Y29:Y30"/>
+    <mergeCell ref="Z29:Z30"/>
+    <mergeCell ref="AA29:AA30"/>
+    <mergeCell ref="R27:R28"/>
+    <mergeCell ref="S27:S28"/>
+    <mergeCell ref="AA23:AA24"/>
+    <mergeCell ref="S25:S26"/>
+    <mergeCell ref="T25:T26"/>
+    <mergeCell ref="U25:U26"/>
+    <mergeCell ref="V25:V26"/>
+    <mergeCell ref="W25:W26"/>
+    <mergeCell ref="X25:X26"/>
+    <mergeCell ref="Y25:Y26"/>
+    <mergeCell ref="Z25:Z26"/>
+    <mergeCell ref="AA25:AA26"/>
+    <mergeCell ref="R23:R24"/>
+    <mergeCell ref="S23:S24"/>
+    <mergeCell ref="T23:T24"/>
+    <mergeCell ref="U23:U24"/>
+    <mergeCell ref="V23:V24"/>
+    <mergeCell ref="W23:W24"/>
+    <mergeCell ref="X23:X24"/>
+    <mergeCell ref="Y23:Y24"/>
+    <mergeCell ref="Z23:Z24"/>
+    <mergeCell ref="R19:AA20"/>
+    <mergeCell ref="R21:R22"/>
+    <mergeCell ref="S21:S22"/>
+    <mergeCell ref="T21:T22"/>
+    <mergeCell ref="U21:U22"/>
+    <mergeCell ref="V21:V22"/>
+    <mergeCell ref="W21:W22"/>
+    <mergeCell ref="X21:X22"/>
+    <mergeCell ref="Y21:Y22"/>
+    <mergeCell ref="Z21:Z22"/>
+    <mergeCell ref="AA21:AA22"/>
     <mergeCell ref="E35:P35"/>
     <mergeCell ref="E36:P36"/>
     <mergeCell ref="E37:P37"/>
@@ -1644,6 +1804,118 @@
     <mergeCell ref="J7:J8"/>
     <mergeCell ref="K7:K8"/>
     <mergeCell ref="L7:L8"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="N7:N8"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="O15:O16"/>
+    <mergeCell ref="P15:P16"/>
+    <mergeCell ref="O11:O12"/>
+    <mergeCell ref="N15:N16"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="P11:P12"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="R5:AA6"/>
+    <mergeCell ref="R7:R8"/>
+    <mergeCell ref="S7:S8"/>
+    <mergeCell ref="T7:T8"/>
+    <mergeCell ref="U7:U8"/>
+    <mergeCell ref="V7:V8"/>
+    <mergeCell ref="W7:W8"/>
+    <mergeCell ref="X7:X8"/>
+    <mergeCell ref="Y7:Y8"/>
+    <mergeCell ref="Z7:Z8"/>
+    <mergeCell ref="AA7:AA8"/>
+    <mergeCell ref="R9:R10"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
+    <mergeCell ref="V9:V10"/>
+    <mergeCell ref="W9:W10"/>
+    <mergeCell ref="X9:X10"/>
+    <mergeCell ref="Y9:Y10"/>
+    <mergeCell ref="Z9:Z10"/>
+    <mergeCell ref="AA9:AA10"/>
+    <mergeCell ref="S11:S12"/>
+    <mergeCell ref="T11:T12"/>
+    <mergeCell ref="U11:U12"/>
+    <mergeCell ref="V11:V12"/>
+    <mergeCell ref="W11:W12"/>
+    <mergeCell ref="X11:X12"/>
+    <mergeCell ref="Y11:Y12"/>
+    <mergeCell ref="Z11:Z12"/>
+    <mergeCell ref="AA11:AA12"/>
+    <mergeCell ref="Z13:Z14"/>
+    <mergeCell ref="AA13:AA14"/>
+    <mergeCell ref="X15:X16"/>
+    <mergeCell ref="Y15:Y16"/>
+    <mergeCell ref="Z15:Z16"/>
+    <mergeCell ref="AA15:AA16"/>
+    <mergeCell ref="T13:T14"/>
+    <mergeCell ref="U13:U14"/>
+    <mergeCell ref="V13:V14"/>
+    <mergeCell ref="W13:W14"/>
+    <mergeCell ref="X13:X14"/>
+    <mergeCell ref="Y13:Y14"/>
+    <mergeCell ref="G19:P20"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="K21:K22"/>
+    <mergeCell ref="L21:L22"/>
+    <mergeCell ref="M21:M22"/>
+    <mergeCell ref="N21:N22"/>
+    <mergeCell ref="O21:O22"/>
+    <mergeCell ref="P21:P22"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="K23:K24"/>
+    <mergeCell ref="L23:L24"/>
+    <mergeCell ref="M23:M24"/>
+    <mergeCell ref="N23:N24"/>
+    <mergeCell ref="O23:O24"/>
+    <mergeCell ref="P23:P24"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="K25:K26"/>
+    <mergeCell ref="L25:L26"/>
+    <mergeCell ref="M25:M26"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="O25:O26"/>
+    <mergeCell ref="P25:P26"/>
+    <mergeCell ref="O27:O28"/>
+    <mergeCell ref="P27:P28"/>
+    <mergeCell ref="M29:M30"/>
+    <mergeCell ref="N29:N30"/>
+    <mergeCell ref="O29:O30"/>
+    <mergeCell ref="P29:P30"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="K27:K28"/>
+    <mergeCell ref="L27:L28"/>
+    <mergeCell ref="M27:M28"/>
+    <mergeCell ref="N27:N28"/>
+    <mergeCell ref="T27:T28"/>
+    <mergeCell ref="U27:U28"/>
+    <mergeCell ref="V27:V28"/>
+    <mergeCell ref="W27:W28"/>
+    <mergeCell ref="X27:X28"/>
+    <mergeCell ref="Y27:Y28"/>
+    <mergeCell ref="Z27:Z28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
